--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/biobio.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/biobio.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
